--- a/data/trans_orig/IP25A_R_2023-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP25A_R_2023-Provincia-trans_orig.xlsx
@@ -535,13 +535,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que emplean 2 horas o más en ver la televisión en 2023 (tasa de respuesta: 98,91%)</t>
+          <t>Menores según si emplean dos o más horas al día, entre semana y fines de semana, en ver la televisión en 2023 (tasa de respuesta: 98,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>11134</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>6718</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>17007</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>17,36%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>10,47%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>26,51%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>10029</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>5419</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>17675</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>13,69%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>7,4%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>24,12%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>13214</t>
+          <t>7962</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8127</t>
+          <t>4646</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19253</t>
+          <t>12493</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>23242</t>
+          <t>19096</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>15962</t>
+          <t>13164</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>31838</t>
+          <t>26452</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>21,93%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>53011</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>47138</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>57427</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>82,64%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>73,49%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>89,53%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>82</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>63253</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>55607</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>67863</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>86,31%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>75,88%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>92,6%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>66152</t>
+          <t>48519</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>60113</t>
+          <t>43988</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>71239</t>
+          <t>51835</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>83,35%</t>
+          <t>85,9%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>75,74%</t>
+          <t>77,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,76%</t>
+          <t>91,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>129406</t>
+          <t>101530</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>120810</t>
+          <t>94174</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>136686</t>
+          <t>107462</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>84,77%</t>
+          <t>84,17%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,14%</t>
+          <t>78,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,54%</t>
+          <t>89,09%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>64145</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>64145</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>64145</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>96</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>73282</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>73282</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>73282</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>79366</t>
+          <t>56481</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>79366</t>
+          <t>56481</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>79366</t>
+          <t>56481</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>152648</t>
+          <t>120626</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>152648</t>
+          <t>120626</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>152648</t>
+          <t>120626</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>23081</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>15313</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>31669</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>19,93%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>13,22%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>27,34%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>24599</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>11199</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>36115</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>19,58%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>8,91%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>28,74%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>24852</t>
+          <t>21878</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16635</t>
+          <t>15549</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>34114</t>
+          <t>30151</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>49451</t>
+          <t>44959</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>32049</t>
+          <t>34429</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>64446</t>
+          <t>55613</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>25,85%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>92754</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>84166</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>100522</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>80,07%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>72,66%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>86,78%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>101050</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>89534</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>114450</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>80,42%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>71,26%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>91,09%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>102744</t>
+          <t>77455</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>93482</t>
+          <t>69182</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>110961</t>
+          <t>83784</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>80,52%</t>
+          <t>77,98%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>73,26%</t>
+          <t>69,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,96%</t>
+          <t>84,35%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>203794</t>
+          <t>170210</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>188799</t>
+          <t>159556</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>221196</t>
+          <t>180740</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>80,47%</t>
+          <t>79,11%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>74,55%</t>
+          <t>74,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>84,0%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>115835</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>115835</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>115835</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>140</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>125649</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>125649</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>125649</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>127596</t>
+          <t>99333</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>127596</t>
+          <t>99333</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>127596</t>
+          <t>99333</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>253245</t>
+          <t>215169</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>253245</t>
+          <t>215169</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>253245</t>
+          <t>215169</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3134</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1258</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>6906</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>5,28%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2,12%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>11,63%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>4716</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2099</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>8443</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>8,23%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3,66%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>14,74%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>3619</t>
+          <t>4537</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1352</t>
+          <t>2081</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8016</t>
+          <t>8760</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>8335</t>
+          <t>7671</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4204</t>
+          <t>4357</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13494</t>
+          <t>12423</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,8%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>56243</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>52471</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>58119</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>94,72%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>88,37%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>97,88%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>87</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>52562</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>48835</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>55179</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>91,77%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>85,26%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>96,34%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>63544</t>
+          <t>51067</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>59147</t>
+          <t>46844</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>65811</t>
+          <t>53523</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,07%</t>
+          <t>84,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>116106</t>
+          <t>107311</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>110947</t>
+          <t>102559</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>120237</t>
+          <t>110625</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>89,2%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,21%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>59377</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>59377</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>59377</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>95</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>57278</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>57278</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>57278</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>67163</t>
+          <t>55604</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>67163</t>
+          <t>55604</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>67163</t>
+          <t>55604</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>124441</t>
+          <t>114982</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>124441</t>
+          <t>114982</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>124441</t>
+          <t>114982</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>12609</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>6124</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>21168</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>17,84%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>8,67%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>29,96%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>9791</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>5300</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>15447</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>14,86%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>8,04%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>23,44%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>14374</t>
+          <t>9796</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7019</t>
+          <t>5305</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23653</t>
+          <t>16310</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>24166</t>
+          <t>22405</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>15815</t>
+          <t>14256</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>33990</t>
+          <t>32261</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>23,46%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>58047</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>49488</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>64532</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>82,16%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>70,04%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>91,33%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>74</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>56096</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>50440</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>60587</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>85,14%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>76,56%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>91,96%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>62300</t>
+          <t>57089</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>53021</t>
+          <t>50575</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>69655</t>
+          <t>61580</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>81,25%</t>
+          <t>85,35%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,15%</t>
+          <t>75,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>118395</t>
+          <t>115136</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>108571</t>
+          <t>105280</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>126746</t>
+          <t>123285</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>83,05%</t>
+          <t>83,71%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,16%</t>
+          <t>76,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,91%</t>
+          <t>89,64%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>70656</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>70656</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>70656</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>65887</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>65887</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>65887</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>76674</t>
+          <t>66885</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>76674</t>
+          <t>66885</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>76674</t>
+          <t>66885</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>142561</t>
+          <t>137541</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>142561</t>
+          <t>137541</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>142561</t>
+          <t>137541</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>4648</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2059</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>10609</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>11,74%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>5,2%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>26,8%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>573</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>574</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>2855</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>1,66%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>2524</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>1,61%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>8,27%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>4538</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>1865</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>9720</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>11,14%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>4,58%</t>
-        </is>
-      </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>5111</t>
+          <t>5221</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2472</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10955</t>
+          <t>11243</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,95%</t>
         </is>
       </c>
     </row>
@@ -2205,74 +2205,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>34931</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>28970</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>37520</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>88,26%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>73,2%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>94,8%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>33940</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>31658</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>34513</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>98,34%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>91,73%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>35034</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>33084</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>35608</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>98,39%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>92,91%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>36181</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>30999</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>38854</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>88,86%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>76,13%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>95,42%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>131</t>
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>70121</t>
+          <t>69966</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>64277</t>
+          <t>63944</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>72876</t>
+          <t>72715</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>85,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,71%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>39579</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>34513</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>34513</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>34513</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35608</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35608</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>35608</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>75232</t>
+          <t>75187</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>75232</t>
+          <t>75187</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>75232</t>
+          <t>75187</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2435,72 +2435,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>7282</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>4159</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>11759</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>14,88%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>8,5%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>24,03%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>9670</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>5737</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>14457</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>20,94%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>12,43%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>31,31%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>8239</t>
+          <t>9850</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4305</t>
+          <t>5945</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13287</t>
+          <t>15051</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,65%</t>
+          <t>32,89%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>17909</t>
+          <t>17132</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>12237</t>
+          <t>12125</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>24358</t>
+          <t>23132</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>24,42%</t>
         </is>
       </c>
     </row>
@@ -2548,72 +2548,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>41660</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>37183</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>44783</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>85,12%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>75,97%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>91,5%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>64</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>36497</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>31710</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>40430</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>79,06%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>68,69%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>87,57%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>47947</t>
+          <t>35916</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>42899</t>
+          <t>30715</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>51881</t>
+          <t>39821</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>85,34%</t>
+          <t>78,48%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>76,35%</t>
+          <t>67,11%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>87,01%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>84444</t>
+          <t>77576</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>77995</t>
+          <t>71576</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>90116</t>
+          <t>82583</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>82,5%</t>
+          <t>81,91%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>76,2%</t>
+          <t>75,58%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>87,2%</t>
         </is>
       </c>
     </row>
@@ -2661,57 +2661,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>48942</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>48942</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>48942</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>46167</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>46167</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>46167</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>56186</t>
+          <t>45766</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>56186</t>
+          <t>45766</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>56186</t>
+          <t>45766</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>102353</t>
+          <t>94708</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>102353</t>
+          <t>94708</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>102353</t>
+          <t>94708</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2778,72 +2778,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>25347</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>18173</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>34846</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>18,07%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>12,96%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>24,85%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>27364</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>19387</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>37155</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>22,73%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>16,1%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>30,86%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>26564</t>
+          <t>26076</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>18477</t>
+          <t>19573</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>36879</t>
+          <t>35402</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>53928</t>
+          <t>51423</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>42025</t>
+          <t>40505</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>67853</t>
+          <t>64014</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,75%</t>
         </is>
       </c>
     </row>
@@ -2891,72 +2891,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>114902</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>105403</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>122076</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>81,93%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>75,15%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>87,04%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>132</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>93032</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>83241</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>101009</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>77,27%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>69,14%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>83,9%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>128090</t>
+          <t>92342</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>117775</t>
+          <t>83016</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>136177</t>
+          <t>98845</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>82,82%</t>
+          <t>77,98%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>76,15%</t>
+          <t>70,1%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>88,05%</t>
+          <t>83,47%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>221122</t>
+          <t>207244</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>207197</t>
+          <t>194653</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>233025</t>
+          <t>218162</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>80,39%</t>
+          <t>80,12%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>75,33%</t>
+          <t>75,25%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>84,72%</t>
+          <t>84,34%</t>
         </is>
       </c>
     </row>
@@ -3004,57 +3004,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>140249</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>140249</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>140249</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>170</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>120396</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>120396</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>120396</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>175</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>154654</t>
+          <t>118418</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>154654</t>
+          <t>118418</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>154654</t>
+          <t>118418</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>275050</t>
+          <t>258667</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>275050</t>
+          <t>258667</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>275050</t>
+          <t>258667</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3121,74 +3121,74 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>8776</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>4585</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>14678</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>5,52%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>2,88%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>9,22%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>2987</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>798</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>7763</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>2,28%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>0,61%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>3263</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>925</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>8300</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>2,33%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>0,66%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
         <is>
           <t>5,93%</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>8927</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>4497</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>14487</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>5,71%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>2,87%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>9,26%</t>
-        </is>
-      </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
           <t>17</t>
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>11913</t>
+          <t>12038</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>7203</t>
+          <t>7044</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>18806</t>
+          <t>19337</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,47%</t>
         </is>
       </c>
     </row>
@@ -3234,72 +3234,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>150341</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>144439</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>154532</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>94,48%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>90,78%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>97,12%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>186</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>128029</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>123253</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>130218</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>97,72%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>136710</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>131673</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>139048</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>97,67%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>94,07%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>99,39%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>147510</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>141950</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>151940</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>94,29%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>90,74%</t>
-        </is>
-      </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>275540</t>
+          <t>287052</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>268647</t>
+          <t>279753</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>280250</t>
+          <t>292046</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,64%</t>
         </is>
       </c>
     </row>
@@ -3347,57 +3347,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>159117</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>159117</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>159117</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>190</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>131016</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>131016</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>131016</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>156437</t>
+          <t>139973</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>156437</t>
+          <t>139973</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>156437</t>
+          <t>139973</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>287453</t>
+          <t>299090</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>287453</t>
+          <t>299090</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>287453</t>
+          <t>299090</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3464,62 +3464,62 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>96010</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>81248</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>112983</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>13,76%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>11,64%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>16,19%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>125</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>89730</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>72364</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>107420</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>13,72%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>11,06%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>16,42%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>104325</t>
+          <t>83936</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>87401</t>
+          <t>71183</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>123075</t>
+          <t>99093</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>194055</t>
+          <t>179946</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>171524</t>
+          <t>159367</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>223073</t>
+          <t>204211</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,52%</t>
         </is>
       </c>
     </row>
@@ -3577,67 +3577,67 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>840</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>601891</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>584918</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>616653</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>86,24%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>83,81%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>88,36%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>801</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>564459</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>546769</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>581825</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>86,28%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>83,58%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>88,94%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>840</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>654469</t>
+          <t>534132</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>635719</t>
+          <t>518975</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>671393</t>
+          <t>546885</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>86,25%</t>
+          <t>86,42%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>83,78%</t>
+          <t>83,97%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3652,32 +3652,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>1218928</t>
+          <t>1136024</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1189910</t>
+          <t>1111759</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1241459</t>
+          <t>1156603</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>86,27%</t>
+          <t>86,33%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>84,21%</t>
+          <t>84,48%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
+          <t>87,89%</t>
         </is>
       </c>
     </row>
@@ -3690,57 +3690,57 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>972</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>697901</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>697901</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>697901</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>926</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>654189</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>654189</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>654189</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>972</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>758794</t>
+          <t>618068</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>758794</t>
+          <t>618068</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>758794</t>
+          <t>618068</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3765,17 +3765,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1412983</t>
+          <t>1315970</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1412983</t>
+          <t>1315970</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1412983</t>
+          <t>1315970</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
